--- a/mygui_docking/Project1/x64/Release/sensor_data.xlsx
+++ b/mygui_docking/Project1/x64/Release/sensor_data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>Time Stack</t>
   </si>
@@ -76,12 +76,74 @@
   </si>
   <si>
     <t>2025-07-08 14:56:16</t>
+  </si>
+  <si>
+    <t>2025-07-08 14:59:27</t>
+  </si>
+  <si>
+    <t>2025-07-08 14:59:28</t>
+  </si>
+  <si>
+    <t>2025-07-08 14:59:29</t>
+  </si>
+  <si>
+    <t>2025-07-08 14:59:30</t>
+  </si>
+  <si>
+    <t>2025-07-08 14:59:31</t>
+  </si>
+  <si>
+    <t>2025-07-08 14:59:32</t>
+  </si>
+  <si>
+    <t>2025-07-08 14:59:33</t>
+  </si>
+  <si>
+    <t>2025-07-08 14:59:34</t>
+  </si>
+  <si>
+    <t>2025-07-08 14:59:35</t>
+  </si>
+  <si>
+    <t>2025-07-08 14:59:36</t>
+  </si>
+  <si>
+    <t>2025-07-08 15:00:15</t>
+  </si>
+  <si>
+    <t>2025-07-08 15:00:16</t>
+  </si>
+  <si>
+    <t>2025-07-08 15:00:17</t>
+  </si>
+  <si>
+    <t>2025-07-08 15:00:18</t>
+  </si>
+  <si>
+    <t>2025-07-08 15:00:19</t>
+  </si>
+  <si>
+    <t>2025-07-08 15:00:20</t>
+  </si>
+  <si>
+    <t>2025-07-08 15:00:21</t>
+  </si>
+  <si>
+    <t>2025-07-08 15:00:22</t>
+  </si>
+  <si>
+    <t>2025-07-08 15:00:23</t>
+  </si>
+  <si>
+    <t>2025-07-08 15:00:24</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts>
+	</numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -444,234 +506,292 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B2">
-        <v>-0.42</v>
+        <v>2.3100000000000001</v>
       </c>
       <c r="C2">
-        <v>-3.95</v>
+        <v>-26.09</v>
       </c>
       <c r="D2">
-        <v>-0.47</v>
+        <v>2.3100000000000001</v>
       </c>
       <c r="E2">
-        <v>-4.1399999999999997</v>
+        <v>-26.109999999999999</v>
       </c>
       <c r="F2">
-        <v>-6.44</v>
+        <v>-4.3799999999999999</v>
       </c>
       <c r="G2">
-        <v>-7.72</v>
+        <v>-8.2200000000000006</v>
       </c>
       <c r="H2">
-        <v>-6.44</v>
+        <v>-4.3799999999999999</v>
       </c>
       <c r="I2">
-        <v>-7.72</v>
+        <v>-8.2200000000000006</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B3">
-        <v>-0.47</v>
+        <v>-2.77</v>
       </c>
       <c r="C3">
-        <v>-4.1399999999999997</v>
+        <v>-2.9700000000000002</v>
       </c>
       <c r="D3">
-        <v>-0.47</v>
+        <v>-2.8100000000000001</v>
       </c>
       <c r="E3">
-        <v>-4.1399999999999997</v>
+        <v>-2.7999999999999998</v>
       </c>
       <c r="F3">
-        <v>-3.66</v>
+        <v>-4.3799999999999999</v>
       </c>
       <c r="G3">
-        <v>-7.22</v>
+        <v>-8.2200000000000006</v>
       </c>
       <c r="H3">
-        <v>-3.66</v>
+        <v>-4.3799999999999999</v>
       </c>
       <c r="I3">
-        <v>-7.22</v>
+        <v>-8.2200000000000006</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B4">
-        <v>-6.47</v>
+        <v>-2.8100000000000001</v>
       </c>
       <c r="C4">
-        <v>-11.48</v>
+        <v>-2.7999999999999998</v>
       </c>
       <c r="D4">
-        <v>-6.47</v>
+        <v>-2.8100000000000001</v>
       </c>
       <c r="E4">
-        <v>-11.48</v>
+        <v>-2.7999999999999998</v>
       </c>
       <c r="F4">
-        <v>-3.66</v>
+        <v>-4.2800000000000002</v>
       </c>
       <c r="G4">
-        <v>-7.22</v>
+        <v>-9.3800000000000008</v>
       </c>
       <c r="H4">
-        <v>-3.66</v>
+        <v>-4.2800000000000002</v>
       </c>
       <c r="I4">
-        <v>-7.22</v>
+        <v>-9.3800000000000008</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B5">
-        <v>-8.49</v>
+        <v>-12.779999999999999</v>
       </c>
       <c r="C5">
-        <v>-15.75</v>
+        <v>-26.379999999999999</v>
       </c>
       <c r="D5">
-        <v>-8.34</v>
+        <v>-12.779999999999999</v>
       </c>
       <c r="E5">
-        <v>-15.45</v>
+        <v>-26.390000000000001</v>
       </c>
       <c r="F5">
-        <v>-3.5</v>
+        <v>-4.2800000000000002</v>
       </c>
       <c r="G5">
-        <v>-7.72</v>
+        <v>-9.3800000000000008</v>
       </c>
       <c r="H5">
-        <v>-3.44</v>
+        <v>-4.2800000000000002</v>
       </c>
       <c r="I5">
-        <v>-7.94</v>
+        <v>-9.3800000000000008</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B6">
-        <v>-8.34</v>
+        <v>-16.879999999999999</v>
       </c>
       <c r="C6">
-        <v>-15.45</v>
+        <v>-47.340000000000003</v>
       </c>
       <c r="D6">
-        <v>-8.34</v>
+        <v>-16.59</v>
       </c>
       <c r="E6">
-        <v>-15.45</v>
+        <v>-45.890000000000001</v>
       </c>
       <c r="F6">
-        <v>-3.44</v>
+        <v>-4.2800000000000002</v>
       </c>
       <c r="G6">
-        <v>-7.94</v>
+        <v>-9.3100000000000005</v>
       </c>
       <c r="H6">
-        <v>-3.44</v>
+        <v>-4.2800000000000002</v>
       </c>
       <c r="I6">
-        <v>-7.94</v>
+        <v>-9.3100000000000005</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B7">
-        <v>-7.28</v>
+        <v>-16.59</v>
       </c>
       <c r="C7">
-        <v>-27.95</v>
+        <v>-45.880000000000003</v>
       </c>
       <c r="D7">
-        <v>-7.28</v>
+        <v>-16.59</v>
       </c>
       <c r="E7">
-        <v>-27.95</v>
+        <v>-45.890000000000001</v>
       </c>
       <c r="F7">
-        <v>-3.44</v>
+        <v>-4.2800000000000002</v>
       </c>
       <c r="G7">
-        <v>-7.94</v>
+        <v>-9.3100000000000005</v>
       </c>
       <c r="H7">
-        <v>-3.44</v>
+        <v>-4.2800000000000002</v>
       </c>
       <c r="I7">
-        <v>-7.94</v>
+        <v>-9.3100000000000005</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B8">
-        <v>-9.7799999999999994</v>
+        <v>-17.629999999999999</v>
       </c>
       <c r="C8">
-        <v>-44.08</v>
+        <v>-0.16</v>
       </c>
       <c r="D8">
-        <v>-10.88</v>
+        <v>-17.629999999999999</v>
       </c>
       <c r="E8">
-        <v>-51.14</v>
+        <v>-0.20000000000000001</v>
       </c>
       <c r="F8">
-        <v>-3.59</v>
+        <v>-4.2800000000000002</v>
       </c>
       <c r="G8">
-        <v>-8.1300000000000008</v>
+        <v>-9.3100000000000005</v>
       </c>
       <c r="H8">
-        <v>-3.59</v>
+        <v>-4.2800000000000002</v>
       </c>
       <c r="I8">
-        <v>-8.1300000000000008</v>
+        <v>-9.3100000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B9">
-        <v>-10.88</v>
+        <v>-17.579999999999998</v>
       </c>
       <c r="C9">
-        <v>-51.13</v>
+        <v>6.6600000000000001</v>
       </c>
       <c r="D9">
-        <v>-10.88</v>
+        <v>-17.559999999999999</v>
       </c>
       <c r="E9">
-        <v>-51.14</v>
+        <v>9.6400000000000006</v>
       </c>
       <c r="F9">
-        <v>-3.59</v>
+        <v>-4.0899999999999999</v>
       </c>
       <c r="G9">
-        <v>-8.1300000000000008</v>
+        <v>-9.2200000000000006</v>
       </c>
       <c r="H9">
-        <v>-3.59</v>
+        <v>-4.0899999999999999</v>
       </c>
       <c r="I9">
-        <v>-8.1300000000000008</v>
+        <v>-9.2200000000000006</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10">
+        <v>-17.559999999999999</v>
+      </c>
+      <c r="C10">
+        <v>9.6400000000000006</v>
+      </c>
+      <c r="D10">
+        <v>-17.559999999999999</v>
+      </c>
+      <c r="E10">
+        <v>9.6400000000000006</v>
+      </c>
+      <c r="F10">
+        <v>-4.0899999999999999</v>
+      </c>
+      <c r="G10">
+        <v>-9.2200000000000006</v>
+      </c>
+      <c r="H10">
+        <v>-4.0899999999999999</v>
+      </c>
+      <c r="I10">
+        <v>-9.2200000000000006</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11">
+        <v>-16.350000000000001</v>
+      </c>
+      <c r="C11">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="D11">
+        <v>-16.34</v>
+      </c>
+      <c r="E11">
+        <v>9.7599999999999998</v>
+      </c>
+      <c r="F11">
+        <v>-4.1299999999999999</v>
+      </c>
+      <c r="G11">
+        <v>-9.2200000000000006</v>
+      </c>
+      <c r="H11">
+        <v>-4.1299999999999999</v>
+      </c>
+      <c r="I11">
+        <v>-9.2200000000000006</v>
       </c>
     </row>
   </sheetData>
